--- a/output/pdf_financials_xlsx/ERKA.xlsx
+++ b/output/pdf_financials_xlsx/ERKA.xlsx
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000257</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.020693</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.030013</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.18961</v>
+        <v>-0.189867</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.060496</v>
+        <v>-6.081189</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.3734</v>
+        <v>-4.403413</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-6.396127</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.18961</v>
+        <v>-0.189867</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.060496</v>
+        <v>-6.081189</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.3734</v>
+        <v>-4.403413</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-6.396127</v>
@@ -1088,7 +1088,7 @@
         <v>0.041764</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.455716</v>
       </c>
     </row>
     <row r="35">
@@ -1126,7 +1126,7 @@
         <v>0.041764</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.455716</v>
       </c>
     </row>
     <row r="37">
@@ -1354,7 +1354,7 @@
         <v>0.017484</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.476398</v>
+        <v>0.020682</v>
       </c>
     </row>
     <row r="49">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">

--- a/output/pdf_financials_xlsx/ERKA.xlsx
+++ b/output/pdf_financials_xlsx/ERKA.xlsx
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.011864</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.043825</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.155638</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.069898</v>
       </c>
     </row>
     <row r="68">
@@ -4232,7 +4232,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
